--- a/artfynd/A 31708-2021 artfynd.xlsx
+++ b/artfynd/A 31708-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31708-2021 artfynd.xlsx
+++ b/artfynd/A 31708-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73662424</v>
+        <v>73662422</v>
       </c>
       <c r="B2" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>870025.5462061085</v>
+        <v>870070</v>
       </c>
       <c r="R2" t="n">
-        <v>7312741.948787262</v>
+        <v>7312714</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2018-09-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-09-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73662411</v>
+        <v>98309056</v>
       </c>
       <c r="B3" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rotudden, Nb</t>
+          <t>Vikmyran-Storön, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>870069.549319385</v>
+        <v>870090</v>
       </c>
       <c r="R3" t="n">
-        <v>7312713.964342981</v>
+        <v>7312685</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,22 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-09-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-09-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Anna Jonsson</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,11 +863,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog, basalt</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -902,22 +872,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Via Sture Westerberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73662423</v>
+        <v>98309059</v>
       </c>
       <c r="B4" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,34 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3215</v>
+        <v>504</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rotudden, Nb</t>
+          <t>Vikmyran-Storön, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>870025.5462061085</v>
+        <v>870081</v>
       </c>
       <c r="R4" t="n">
-        <v>7312741.948787262</v>
+        <v>7312693</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,22 +944,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-09-18</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-09-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Anna Jonsson</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,11 +965,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog, basalt</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1019,22 +974,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Via Sture Westerberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73662422</v>
+        <v>73662423</v>
       </c>
       <c r="B5" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>504</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>870069.549319385</v>
+        <v>870026</v>
       </c>
       <c r="R5" t="n">
-        <v>7312713.964342981</v>
+        <v>7312742</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,19 +1049,9 @@
           <t>2018-09-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-09-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,6 +1080,836 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129755943</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Storön, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>869852</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7312682</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>73662411</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rotudden, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>870070</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7312714</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2018-09-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog, basalt</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>73662424</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rotudden, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>870026</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7312742</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2018-09-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog, basalt</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>73662428</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rotudden, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>870023</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7312679</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2018-09-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Hällmarksblandskog, rikt,tallöverståndare, basalt</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>101374242</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Storön 988, Kalix, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>869821</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7312698</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-06-03</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-06-03</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>98309062</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vikmyran-Storön, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>870078</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7312682</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Anna Jonsson</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Via Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>98308857</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99155</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vikmyran-Storön, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>871033</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7312723</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-06-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-06-10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Rasmus Häggqvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>98308869</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99155</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vikmyran-Storön, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>870923</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7312746</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-06-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-06-10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Rasmus Häggqvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
